--- a/excel/Debitum.xlsx
+++ b/excel/Debitum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Debitum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594CBF54-5CA5-4B48-BAB4-B5C996BC1BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E51E50-7799-4BB3-B3A6-532C96F3EA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -490,13 +490,16 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -508,27 +511,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2033,44 +2026,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="32" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="37" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
       <c r="P1" s="8"/>
-      <c r="Q1" s="29" t="s">
+      <c r="Q1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="29" t="s">
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="31"/>
-      <c r="W1" s="32" t="s">
+      <c r="V1" s="38"/>
+      <c r="W1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
       <c r="AA1" s="4" t="s">
         <v>39</v>
       </c>
@@ -2201,7 +2194,7 @@
       </c>
       <c r="K3" s="20">
         <f ca="1">'LV0000106516'!B12</f>
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L3" s="2" t="str">
         <f ca="1">'LV0000106516'!P3</f>
@@ -2220,47 +2213,47 @@
         <v>0</v>
       </c>
       <c r="P3" s="9"/>
-      <c r="Q3" s="39">
+      <c r="Q3" s="29">
         <f>Pinigai!I2</f>
         <v>240</v>
       </c>
-      <c r="R3" s="39">
+      <c r="R3" s="29">
         <f>SUM(H3:H100)-U3</f>
         <v>253.25</v>
       </c>
-      <c r="S3" s="40">
+      <c r="S3" s="30">
         <f>Pinigai!H2</f>
         <v>0.89</v>
       </c>
-      <c r="T3" s="40">
+      <c r="T3" s="30">
         <f>W3-R3</f>
         <v>0</v>
       </c>
-      <c r="U3" s="39">
+      <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
         <v>71.63</v>
       </c>
-      <c r="V3" s="39">
+      <c r="V3" s="29">
         <f>SUM(N3:N100)-AA3</f>
         <v>12.36</v>
       </c>
-      <c r="W3" s="40">
+      <c r="W3" s="30">
         <f>Q3+S3+V3</f>
         <v>253.25</v>
       </c>
-      <c r="X3" s="40">
+      <c r="X3" s="30">
         <f>W3-Q3</f>
         <v>13.25</v>
       </c>
-      <c r="Y3" s="41">
+      <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
         <v>5.5208333333333331E-2</v>
       </c>
-      <c r="Z3" s="42">
+      <c r="Z3" s="32">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.11189493536949158</v>
-      </c>
-      <c r="AA3" s="40">
+        <v>0.11002857089042661</v>
+      </c>
+      <c r="AA3" s="30">
         <f>SUM(O3:O100)</f>
         <v>0</v>
       </c>
@@ -2311,7 +2304,7 @@
       </c>
       <c r="K4" s="20">
         <f ca="1">'LV0000106920'!B12</f>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L4" s="2" t="str">
         <f ca="1">'LV0000106920'!P3</f>
@@ -2330,17 +2323,16 @@
         <v>0</v>
       </c>
       <c r="P4" s="9"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="36"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="18"/>
+      <c r="Z4" s="18"/>
       <c r="AC4" s="3" t="str">
         <f ca="1">'LV0000106920'!Z3</f>
         <v/>
@@ -2586,7 +2578,7 @@
       </c>
       <c r="K8" s="20">
         <f ca="1">'LV0000109064'!B12</f>
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L8" s="2" t="str">
         <f ca="1">'LV0000109064'!P3</f>
@@ -2652,7 +2644,7 @@
       </c>
       <c r="K9" s="20">
         <f ca="1">'LV0000110047'!B12</f>
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L9" s="2" t="str">
         <f ca="1">'LV0000110047'!P3</f>
@@ -2718,7 +2710,7 @@
       </c>
       <c r="K10" s="20">
         <f ca="1">'LV0000110328'!B12</f>
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="str">
         <f ca="1">'LV0000110328'!P3</f>
@@ -2784,7 +2776,7 @@
       </c>
       <c r="K11" s="20">
         <f ca="1">'LV0000111102'!B12</f>
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L11" s="2" t="str">
         <f ca="1">'LV0000111102'!P3</f>
@@ -2849,7 +2841,7 @@
       </c>
       <c r="K12" s="20">
         <f ca="1">'LV0000111060'!B12</f>
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L12" s="2" t="str">
         <f ca="1">'LV0000111060'!P3</f>
@@ -2914,7 +2906,7 @@
       </c>
       <c r="K13" s="20">
         <f ca="1">'LV0000111698'!B12</f>
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L13" s="2" t="str">
         <f ca="1">'LV0000111698'!P3</f>
@@ -2979,7 +2971,7 @@
       </c>
       <c r="K14" s="20">
         <f ca="1">'LV0000111847'!B12</f>
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="L14" s="2" t="str">
         <f ca="1">'LV0000111847'!P3</f>
@@ -3044,7 +3036,7 @@
       </c>
       <c r="K15" s="20">
         <f ca="1">'LV0000112340'!B12</f>
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="L15" s="2" t="str">
         <f ca="1">'LV0000112340'!P3</f>
@@ -3109,7 +3101,7 @@
       </c>
       <c r="K16" s="20">
         <f ca="1">'LV0000112639'!B12</f>
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L16" s="2" t="str">
         <f ca="1">'LV0000112639'!P3</f>
@@ -3332,12 +3324,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="W1:Z1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
     <cfRule type="expression" dxfId="59" priority="21">
@@ -3405,29 +3397,29 @@
       <c r="B1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3806,7 +3798,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -4734,29 +4726,29 @@
       <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -5145,7 +5137,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -6077,29 +6069,29 @@
       <c r="B1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7428,29 +7420,29 @@
       <c r="B1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8757,29 +8749,29 @@
       <c r="B1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10106,29 +10098,29 @@
       <c r="B1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10547,7 +10539,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D12" s="13">
         <v>46203</v>
@@ -11485,29 +11477,29 @@
       <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11925,7 +11917,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="13">
         <v>46203</v>
@@ -14405,7 +14397,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -14448,29 +14440,29 @@
       <c r="B1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -14799,7 +14791,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -15728,29 +15720,29 @@
       <c r="B1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -16079,7 +16071,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -17008,29 +17000,29 @@
       <c r="B1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -17369,7 +17361,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -18297,29 +18289,29 @@
       <c r="B1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18668,7 +18660,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -19597,29 +19589,29 @@
       <c r="B1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -19968,7 +19960,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -20896,29 +20888,29 @@
       <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -21277,7 +21269,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -22205,29 +22197,29 @@
       <c r="B1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -22596,7 +22588,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>

--- a/excel/Debitum.xlsx
+++ b/excel/Debitum.xlsx
@@ -1,35 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Debitum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Debitum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C35244F-9470-4415-AA34-2FE7032AFDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78BA0FE-3A7E-4C4D-AE28-AE53CD5AD1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="LV0000112548" sheetId="40" r:id="rId3"/>
-    <sheet name="LV0000112639" sheetId="39" r:id="rId4"/>
-    <sheet name="LV0000112340" sheetId="38" r:id="rId5"/>
-    <sheet name="LV0000111847" sheetId="37" r:id="rId6"/>
-    <sheet name="LV0000111698" sheetId="36" r:id="rId7"/>
-    <sheet name="LV0000111060" sheetId="31" r:id="rId8"/>
-    <sheet name="LV0000111102" sheetId="34" r:id="rId9"/>
-    <sheet name="LV0000110328" sheetId="33" r:id="rId10"/>
-    <sheet name="LV0000110047" sheetId="32" r:id="rId11"/>
-    <sheet name="LV0000109064" sheetId="35" r:id="rId12"/>
-    <sheet name="LV0000108736" sheetId="30" r:id="rId13"/>
-    <sheet name="LV0000107886" sheetId="29" r:id="rId14"/>
-    <sheet name="LV0000107902" sheetId="28" r:id="rId15"/>
-    <sheet name="LV0000106920" sheetId="27" r:id="rId16"/>
-    <sheet name="LV0000106516" sheetId="26" r:id="rId17"/>
+    <sheet name="LV0000112365" sheetId="41" r:id="rId3"/>
+    <sheet name="LV0000112548" sheetId="40" r:id="rId4"/>
+    <sheet name="LV0000112639" sheetId="39" r:id="rId5"/>
+    <sheet name="LV0000112340" sheetId="38" r:id="rId6"/>
+    <sheet name="LV0000111847" sheetId="37" r:id="rId7"/>
+    <sheet name="LV0000111698" sheetId="36" r:id="rId8"/>
+    <sheet name="LV0000111060" sheetId="31" r:id="rId9"/>
+    <sheet name="LV0000111102" sheetId="34" r:id="rId10"/>
+    <sheet name="LV0000110328" sheetId="33" r:id="rId11"/>
+    <sheet name="LV0000110047" sheetId="32" r:id="rId12"/>
+    <sheet name="LV0000109064" sheetId="35" r:id="rId13"/>
+    <sheet name="LV0000108736" sheetId="30" r:id="rId14"/>
+    <sheet name="LV0000107886" sheetId="29" r:id="rId15"/>
+    <sheet name="LV0000107902" sheetId="28" r:id="rId16"/>
+    <sheet name="LV0000106920" sheetId="27" r:id="rId17"/>
+    <sheet name="LV0000106516" sheetId="26" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="83">
   <si>
     <t>Paskola</t>
   </si>
@@ -296,6 +297,12 @@
   <si>
     <t>bdb3036f-f951-45a6-b18b-b9271bd2431c</t>
   </si>
+  <si>
+    <t>44050fe8-efc4-4b40-b065-7643731bd5d6</t>
+  </si>
+  <si>
+    <t>LV0000112365</t>
+  </si>
 </sst>
 </file>
 
@@ -425,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -509,12 +516,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -541,7 +542,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="68">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1024,7 +1053,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A85772-560D-4DD6-8991-EEABBB7E4D47}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC2F6888-FF62-47FE-BE5A-AFC6976A858E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1080,7 +1109,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD5FFF8B-1379-4B10-B33C-A47BA2D2CC74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75EB44B2-BE82-4DA4-BC24-43C3B551A32C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1136,7 +1165,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37793A37-C294-4BBF-AFF5-91D3103E335B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD5FFF8B-1379-4B10-B33C-A47BA2D2CC74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1192,7 +1221,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C5A88B-4060-4282-83A5-D6E7B6B546F3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37793A37-C294-4BBF-AFF5-91D3103E335B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1248,7 +1277,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DADCB68-DE8D-4EE6-9D9A-DBE9E3DCE994}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C5A88B-4060-4282-83A5-D6E7B6B546F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1304,6 +1333,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DADCB68-DE8D-4EE6-9D9A-DBE9E3DCE994}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B7AD05-6D99-4CF8-9B83-1713B22C4BAD}"/>
             </a:ext>
           </a:extLst>
@@ -1339,7 +1424,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1416,7 +1501,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{046CB6E9-D945-4CB0-B9DC-5E1FA0789772}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A85772-560D-4DD6-8991-EEABBB7E4D47}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1472,7 +1557,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC4BB32B-7081-4A26-A0A3-2D3872B1A130}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{046CB6E9-D945-4CB0-B9DC-5E1FA0789772}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1528,7 +1613,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{041647A0-20DA-4A1B-98FB-99C8881D24BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC4BB32B-7081-4A26-A0A3-2D3872B1A130}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1584,7 +1669,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBA8F36F-B12B-4557-9C88-75248AD4D68B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{041647A0-20DA-4A1B-98FB-99C8881D24BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1640,7 +1725,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC6D99D1-1FE6-4FDC-846A-926D9CDC3B61}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBA8F36F-B12B-4557-9C88-75248AD4D68B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1696,7 +1781,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B598674F-7A43-41D0-8AF4-A018C402C65E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC6D99D1-1FE6-4FDC-846A-926D9CDC3B61}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1752,7 +1837,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6B3423C-AFA6-48B1-A837-B342809E7546}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B598674F-7A43-41D0-8AF4-A018C402C65E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1808,7 +1893,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75EB44B2-BE82-4DA4-BC24-43C3B551A32C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6B3423C-AFA6-48B1-A837-B342809E7546}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2123,44 +2208,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="35" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="41" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
       <c r="P1" s="8"/>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="38" t="s">
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="35" t="s">
+      <c r="V1" s="38"/>
+      <c r="W1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
       <c r="AA1" s="4" t="s">
         <v>39</v>
       </c>
@@ -2291,7 +2376,7 @@
       </c>
       <c r="K3" s="20">
         <f ca="1">'LV0000106516'!B12</f>
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="L3" s="2" t="str">
         <f ca="1">'LV0000106516'!P3</f>
@@ -2303,7 +2388,7 @@
       </c>
       <c r="N3" s="3">
         <f>'LV0000106516'!L3</f>
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="O3" s="3">
         <f>'LV0000106516'!M3</f>
@@ -2316,7 +2401,7 @@
       </c>
       <c r="R3" s="29">
         <f>SUM(H3:H100)-U3</f>
-        <v>275.64</v>
+        <v>275.77999999999997</v>
       </c>
       <c r="S3" s="30">
         <f>Pinigai!H2</f>
@@ -2324,31 +2409,31 @@
       </c>
       <c r="T3" s="30">
         <f>W3-R3</f>
-        <v>-4.0000000000020464E-2</v>
+        <v>2.5900000000000318</v>
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
-        <v>71.63</v>
+        <v>91.63</v>
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N100)-AA3</f>
-        <v>14.710000000000003</v>
+        <v>17.479999999999997</v>
       </c>
       <c r="W3" s="30">
         <f>Q3+S3+V3</f>
-        <v>275.59999999999997</v>
+        <v>278.37</v>
       </c>
       <c r="X3" s="30">
         <f>W3-Q3</f>
-        <v>15.599999999999966</v>
+        <v>18.370000000000005</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>5.9999999999999866E-2</v>
+        <v>7.0653846153846178E-2</v>
       </c>
       <c r="Z3" s="32">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12504064440727236</v>
+        <v>0.12628324627876283</v>
       </c>
       <c r="AA3" s="30">
         <f>SUM(O3:O100)</f>
@@ -2395,13 +2480,13 @@
         <f>'LV0000106920'!B11</f>
         <v>46286</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="6">
         <f>'LV0000106920'!O3</f>
-        <v/>
-      </c>
-      <c r="K4" s="20">
+        <v>46258</v>
+      </c>
+      <c r="K4" s="20" t="str">
         <f ca="1">'LV0000106920'!B12</f>
-        <v>49</v>
+        <v/>
       </c>
       <c r="L4" s="2" t="str">
         <f ca="1">'LV0000106920'!P3</f>
@@ -2409,11 +2494,11 @@
       </c>
       <c r="M4" s="3">
         <f>'LV0000106920'!K3</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N4" s="3">
         <f>'LV0000106920'!L3</f>
-        <v>1.8099999999999998</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="O4" s="3">
         <f>'LV0000106920'!M3</f>
@@ -2489,7 +2574,7 @@
       </c>
       <c r="N5" s="3">
         <f>'LV0000107902'!L3</f>
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O5" s="3">
         <f>'LV0000107902'!M3</f>
@@ -2675,7 +2760,7 @@
       </c>
       <c r="K8" s="20">
         <f ca="1">'LV0000109064'!B12</f>
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="L8" s="2" t="str">
         <f ca="1">'LV0000109064'!P3</f>
@@ -2687,7 +2772,7 @@
       </c>
       <c r="N8" s="3">
         <f>'LV0000109064'!L3</f>
-        <v>1.3299999999999998</v>
+        <v>1.5499999999999998</v>
       </c>
       <c r="O8" s="3">
         <f>'LV0000109064'!M3</f>
@@ -2741,7 +2826,7 @@
       </c>
       <c r="K9" s="20">
         <f ca="1">'LV0000110047'!B12</f>
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="L9" s="2" t="str">
         <f ca="1">'LV0000110047'!P3</f>
@@ -2753,7 +2838,7 @@
       </c>
       <c r="N9" s="3">
         <f>'LV0000110047'!L3</f>
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="O9" s="3">
         <f>'LV0000110047'!M3</f>
@@ -2807,7 +2892,7 @@
       </c>
       <c r="K10" s="20">
         <f ca="1">'LV0000110328'!B12</f>
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="L10" s="2" t="str">
         <f ca="1">'LV0000110328'!P3</f>
@@ -2819,7 +2904,7 @@
       </c>
       <c r="N10" s="3">
         <f>'LV0000110328'!L3</f>
-        <v>0.98</v>
+        <v>1.21</v>
       </c>
       <c r="O10" s="3">
         <f>'LV0000110328'!M3</f>
@@ -2873,7 +2958,7 @@
       </c>
       <c r="K11" s="20">
         <f ca="1">'LV0000111102'!B12</f>
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="L11" s="2" t="str">
         <f ca="1">'LV0000111102'!P3</f>
@@ -2885,7 +2970,7 @@
       </c>
       <c r="N11" s="3">
         <f>'LV0000111102'!L3</f>
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="O11" s="3">
         <f>'LV0000111102'!M3</f>
@@ -2938,7 +3023,7 @@
       </c>
       <c r="K12" s="20">
         <f ca="1">'LV0000111060'!B12</f>
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="L12" s="2" t="str">
         <f ca="1">'LV0000111060'!P3</f>
@@ -2950,7 +3035,7 @@
       </c>
       <c r="N12" s="3">
         <f>'LV0000111060'!L3</f>
-        <v>0.55000000000000004</v>
+        <v>0.76</v>
       </c>
       <c r="O12" s="3">
         <f>'LV0000111060'!M3</f>
@@ -3003,7 +3088,7 @@
       </c>
       <c r="K13" s="20">
         <f ca="1">'LV0000111698'!B12</f>
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="L13" s="2" t="str">
         <f ca="1">'LV0000111698'!P3</f>
@@ -3015,7 +3100,7 @@
       </c>
       <c r="N13" s="3">
         <f>'LV0000111698'!L3</f>
-        <v>0.58000000000000007</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="O13" s="3">
         <f>'LV0000111698'!M3</f>
@@ -3068,7 +3153,7 @@
       </c>
       <c r="K14" s="20">
         <f ca="1">'LV0000111847'!B12</f>
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="L14" s="2" t="str">
         <f ca="1">'LV0000111847'!P3</f>
@@ -3080,7 +3165,7 @@
       </c>
       <c r="N14" s="3">
         <f>'LV0000111847'!L3</f>
-        <v>0.33999999999999997</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="O14" s="3">
         <f>'LV0000111847'!M3</f>
@@ -3133,7 +3218,7 @@
       </c>
       <c r="K15" s="20">
         <f ca="1">'LV0000112340'!B12</f>
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="L15" s="2" t="str">
         <f ca="1">'LV0000112340'!P3</f>
@@ -3145,7 +3230,7 @@
       </c>
       <c r="N15" s="3">
         <f>'LV0000112340'!L3</f>
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="O15" s="3">
         <f>'LV0000112340'!M3</f>
@@ -3198,7 +3283,7 @@
       </c>
       <c r="K16" s="20">
         <f ca="1">'LV0000112639'!B12</f>
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="L16" s="2" t="str">
         <f ca="1">'LV0000112639'!P3</f>
@@ -3210,7 +3295,7 @@
       </c>
       <c r="N16" s="3">
         <f>'LV0000112639'!L3</f>
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="O16" s="3">
         <f>'LV0000112639'!M3</f>
@@ -3263,7 +3348,7 @@
       </c>
       <c r="K17" s="20">
         <f ca="1">'LV0000112548'!B12</f>
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="L17" s="2" t="str">
         <f ca="1">'LV0000112548'!P3</f>
@@ -3275,7 +3360,7 @@
       </c>
       <c r="N17" s="3">
         <f>'LV0000112548'!L3</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O17" s="3">
         <f>'LV0000112548'!M3</f>
@@ -3287,22 +3372,69 @@
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="AC18" s="1"/>
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6">
+        <f>'LV0000112365'!B9</f>
+        <v>46258</v>
+      </c>
+      <c r="C18" s="22" t="str">
+        <f>'LV0000112365'!B1</f>
+        <v>LV0000112365</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f>'LV0000112365'!B2</f>
+        <v>Latvia</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>'LV0000112365'!B4</f>
+        <v>Notes</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f>'LV0000112365'!B8</f>
+        <v>1 m. 4 mėn. 27 d.</v>
+      </c>
+      <c r="G18" s="7">
+        <f>'LV0000112365'!B15</f>
+        <v>0.125</v>
+      </c>
+      <c r="H18" s="3">
+        <f>'LV0000112365'!B16</f>
+        <v>20.14</v>
+      </c>
+      <c r="I18" s="6">
+        <f>'LV0000112365'!B11</f>
+        <v>46772</v>
+      </c>
+      <c r="J18" s="6" t="str">
+        <f>'LV0000112365'!O3</f>
+        <v/>
+      </c>
+      <c r="K18" s="20">
+        <f ca="1">'LV0000112365'!B12</f>
+        <v>506</v>
+      </c>
+      <c r="L18" s="2" t="str">
+        <f ca="1">'LV0000112365'!P3</f>
+        <v/>
+      </c>
+      <c r="M18" s="3">
+        <f>'LV0000112365'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <f>'LV0000112365'!L3</f>
+        <v>0.04</v>
+      </c>
+      <c r="O18" s="3">
+        <f>'LV0000112365'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
+        <f>'LV0000112639'!Z5</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -3476,20 +3608,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
-    <cfRule type="expression" dxfId="63" priority="21">
+    <cfRule type="expression" dxfId="67" priority="21">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="22">
+    <cfRule type="expression" dxfId="66" priority="22">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC17">
-    <cfRule type="expression" dxfId="61" priority="1">
+  <conditionalFormatting sqref="AC3:AC18">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>$AC3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC27">
-    <cfRule type="expression" dxfId="60" priority="2">
+    <cfRule type="expression" dxfId="64" priority="2">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3509,6 +3641,7 @@
     <hyperlink ref="C15" location="'LV0000112340'!A1" display="'LV0000112340'!A1" xr:uid="{B735E935-BB57-4D32-830D-91A0AE87CC0C}"/>
     <hyperlink ref="C16" location="'LV0000112639'!A1" display="'LV0000112639'!A1" xr:uid="{90B0DC3A-A102-4740-81BC-6E1A14229BD2}"/>
     <hyperlink ref="C17" location="'LV0000112548'!A1" display="'LV0000112548'!A1" xr:uid="{8AB69B64-407A-48D5-9211-BEE3D8EED0EF}"/>
+    <hyperlink ref="C18" location="'LV0000112548'!A1" display="'LV0000112548'!A1" xr:uid="{48F27DAE-9E48-4440-BF1E-61912A73A2E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3516,6 +3649,1335 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50F530F-70D3-4179-810B-A748738D37FC}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="15" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="15" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="13">
+        <v>46142</v>
+      </c>
+      <c r="E3" s="13">
+        <v>46142</v>
+      </c>
+      <c r="F3" s="20">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.99</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="14"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46128</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-21.84</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="13">
+        <v>46171</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46171</v>
+      </c>
+      <c r="F4" s="20">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46142</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="13">
+        <v>46203</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46203</v>
+      </c>
+      <c r="F5" s="20">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46171</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="13">
+        <v>46234</v>
+      </c>
+      <c r="E6" s="13">
+        <v>46234</v>
+      </c>
+      <c r="F6" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46203</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E7" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F7" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46234</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>1 m. 0 mėn. 12 d.</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46265</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46128</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="15"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46125</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="15"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46505</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="15"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="20">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>239</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="15"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="15"/>
+      <c r="N13" s="14"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="25"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="15"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="3">
+        <v>21.84</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="13"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="15"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="13"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="15"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="13"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="15"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="13"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="15"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="13"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="15"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="13"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="15"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="13"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="15"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="13"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="15"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="13"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="15"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="13"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="15"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="13"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="15"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="13"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="15"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="13"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="15"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="13"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="15"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="13"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="15"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="13"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="15"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="13"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="15"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="13"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="15"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="13"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="15"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="13"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="15"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="13"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="15"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="13"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="15"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="13"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="15"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="13"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="15"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="13"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="15"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="13"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="15"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="13"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="15"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="13"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="15"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="13"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="15"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="13"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="15"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="13"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="15"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="13"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="15"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="13"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="15"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="13"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="15"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="13"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="15"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="13"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="26"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.99</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="39" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="37" priority="9">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="36" priority="10">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDA6F67-985C-4768-BD4D-EDE383AEA945}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3542,29 +5004,29 @@
       <c r="B1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3644,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -3656,7 +5118,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.98</v>
+        <v>1.21</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -3725,7 +5187,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -3749,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
@@ -3797,7 +5259,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -3840,15 +5302,24 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>0 m. 6 mėn. 6 d.</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="D8" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E8" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
@@ -3878,11 +5349,11 @@
       <c r="J9" s="15"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -3943,7 +5414,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -4807,7 +6278,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.98</v>
+        <v>1.21</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -4844,7 +6315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873C85DF-B0F2-44DE-8D3A-4838A53EDA3D}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4871,29 +6342,29 @@
       <c r="B1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -4985,7 +6456,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -5078,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>
@@ -5126,7 +6597,7 @@
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -5205,15 +6676,25 @@
       <c r="B9" s="6">
         <v>46064</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="D9" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F9" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
       <c r="J9" s="15"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
@@ -5243,11 +6724,11 @@
       <c r="J10" s="15"/>
       <c r="X10" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y10" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -5282,7 +6763,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -6146,7 +7627,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -6183,7 +7664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C73AE8D-71CD-4B37-8927-10E7D3C24754}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6210,29 +7691,29 @@
       <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -6312,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -6324,7 +7805,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.3299999999999998</v>
+        <v>1.5499999999999998</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -6381,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I4" s="3">
         <v>0</v>
@@ -6393,7 +7874,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -6429,7 +7910,7 @@
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -6580,15 +8061,25 @@
       <c r="B10" s="6">
         <v>46013</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="D10" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E10" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F10" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
       <c r="J10" s="15"/>
       <c r="X10" s="6">
         <f t="shared" si="1"/>
@@ -6618,11 +8109,11 @@
       <c r="J11" s="15"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y11" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -6631,7 +8122,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -7495,7 +8986,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.3299999999999998</v>
+        <v>1.5499999999999998</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -7533,7 +9024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241F0F01-4188-44EC-8BB0-625647DD9250}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -7563,29 +9054,29 @@
       <c r="B1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8884,7 +10375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F970090C-ED9C-4156-B8D2-0D82F3DE697D}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8914,29 +10405,29 @@
       <c r="B1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10216,7 +11707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E524BB66-CDBB-4A5C-BDD5-6A761E934230}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10246,29 +11737,29 @@
       <c r="B1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10360,7 +11851,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -10368,7 +11859,7 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.11838628649711608</v>
+        <v>0.11771559119224548</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
@@ -10594,7 +12085,7 @@
         <v>30</v>
       </c>
       <c r="H9" s="3">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -10632,7 +12123,7 @@
       </c>
       <c r="Y10" s="3">
         <f t="shared" si="2"/>
-        <v>30.26</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -11531,7 +13022,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -11568,8 +13059,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D71776B-CEAC-4360-A7CD-7A59F308D19B}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11595,29 +13089,29 @@
       <c r="B1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11705,31 +13199,31 @@
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.8099999999999998</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="str">
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>0.11158277392387392</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
+        <v>46258</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2" t="str">
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>-28</v>
       </c>
       <c r="T3" s="14"/>
       <c r="X3" s="6">
@@ -12034,9 +13528,9 @@
       <c r="A12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="20" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>49</v>
+        <v/>
       </c>
       <c r="D12" s="13">
         <v>46203</v>
@@ -12086,7 +13580,7 @@
       <c r="H13" s="2">
         <v>0.18</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="3">
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -12103,15 +13597,25 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="25"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="D14" s="13">
+        <v>46258</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46258</v>
+      </c>
+      <c r="F14" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
       <c r="J14" s="15"/>
       <c r="X14" s="6">
         <f t="shared" si="1"/>
@@ -12148,11 +13652,11 @@
       <c r="Q15" s="17"/>
       <c r="X15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46258</v>
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -12916,11 +14420,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.8099999999999998</v>
+        <v>1.9499999999999997</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -12957,7 +14461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3FE9AB-D170-4AA6-8FF9-C3077023F2B7}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12984,29 +14488,29 @@
       <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -13098,7 +14602,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -13403,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="2">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I11" s="3">
         <v>0</v>
@@ -13424,7 +14928,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D12" s="13">
         <v>46203</v>
@@ -13452,7 +14956,7 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -13491,15 +14995,25 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="25"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="D14" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46265</v>
+      </c>
+      <c r="F14" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
       <c r="J14" s="15"/>
       <c r="X14" s="6">
         <f t="shared" si="1"/>
@@ -13536,11 +15050,11 @@
       <c r="Q15" s="17"/>
       <c r="X15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -14308,7 +15822,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -15925,14 +17439,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>275.59999999999997</v>
+        <v>278.37</v>
       </c>
     </row>
   </sheetData>
@@ -15942,7 +17456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7C17D1-1C48-4F44-A336-704CA12C8750}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BBB8EB8-C653-4CFD-8FC0-5A474A16F5BC}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15966,31 +17480,31 @@
         <v>59</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -15999,53 +17513,53 @@
       <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="34" t="s">
+      <c r="K2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="N2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="O2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="P2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="Q2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="X2" s="34" t="s">
+      <c r="X2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="34" t="s">
+      <c r="Y2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" s="34" t="s">
+      <c r="Z2" s="10" t="s">
         <v>53</v>
       </c>
     </row>
@@ -16056,15 +17570,25 @@
       <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="20" t="str">
+      <c r="D3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="15"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -16072,7 +17596,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -16097,11 +17621,11 @@
       <c r="T3" s="14"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-22.39</v>
+        <v>-20.14</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -16127,11 +17651,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -16139,7 +17663,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -16214,7 +17738,7 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 11 mėn. 23 d.</v>
+        <v>1 m. 4 mėn. 27 d.</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -16240,7 +17764,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="6">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -16266,7 +17790,7 @@
         <v>62</v>
       </c>
       <c r="B10" s="6">
-        <v>46211</v>
+        <v>46205</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -16292,7 +17816,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6">
-        <v>46594</v>
+        <v>46772</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="6"/>
@@ -16319,7 +17843,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>357</v>
+        <v>506</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -16390,7 +17914,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="7">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="6"/>
@@ -16423,7 +17947,7 @@
         <v>64</v>
       </c>
       <c r="B16" s="3">
-        <v>22.39</v>
+        <v>20.14</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="6"/>
@@ -17183,7 +18707,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -17216,11 +18740,1301 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7C17D1-1C48-4F44-A336-704CA12C8750}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="15" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="15" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E3" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F3" s="20">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.2</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="14"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46237</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-22.39</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="20" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46265</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="20" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="15"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 11 mėn. 23 d.</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46237</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="15"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46211</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="15"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46594</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="15"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="20">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>328</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="15"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="15"/>
+      <c r="N13" s="14"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="25"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="15"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="3">
+        <v>22.39</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="13"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="15"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="13"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="15"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="13"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="15"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="13"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="15"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="13"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="15"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="13"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="15"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="13"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="15"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="13"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="15"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="13"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="15"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="13"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="15"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="13"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="15"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="13"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="15"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="13"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="15"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="13"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="15"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="13"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="15"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="13"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="15"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="13"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="15"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="13"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="15"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="13"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="15"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="13"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="15"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="13"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="15"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="13"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="15"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="13"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="15"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="13"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="15"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="13"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="15"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="13"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="15"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="13"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="15"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="13"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="15"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="13"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="15"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="13"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="15"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="13"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="15"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="13"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="15"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="13"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="15"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="13"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="15"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="13"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="15"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="13"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="26"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="63" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="61" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="60" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99A9371-01E4-44C5-B1C3-D248C92A6B32}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17247,29 +20061,29 @@
       <c r="B1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -17361,7 +20175,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -17404,15 +20218,25 @@
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -17442,11 +20266,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -17608,7 +20432,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -18472,7 +21296,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -18510,7 +21334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810181EE-D5B3-466D-8952-127372E3C737}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18537,29 +21361,29 @@
       <c r="B1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18651,7 +21475,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -18694,15 +21518,25 @@
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -18732,11 +21566,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -18898,7 +21732,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -19762,7 +22596,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -19800,7 +22634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BFA3639-8ED4-49FC-A638-3EE50E456BE1}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19827,29 +22661,29 @@
       <c r="B1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -19929,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -19941,7 +22775,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.33999999999999997</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -20010,7 +22844,7 @@
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -20020,15 +22854,25 @@
       <c r="B5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="20" t="str">
+      <c r="D5" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F5" s="20">
         <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -20058,11 +22902,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -20198,7 +23042,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -21062,7 +23906,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.33999999999999997</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -21099,7 +23943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB541E5F-C38A-4FC0-99B3-68CD33C3421B}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21126,29 +23970,29 @@
       <c r="B1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -21240,7 +24084,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.58000000000000007</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -21355,15 +24199,25 @@
       <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="D6" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E6" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F6" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -21389,11 +24243,11 @@
       <c r="J7" s="15"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -21507,7 +24361,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -22371,7 +25225,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.58000000000000007</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -22409,7 +25263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1601E0CD-BB32-4316-A11E-B1A27ED36E9F}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22436,29 +25290,29 @@
       <c r="B1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -22550,7 +25404,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.55000000000000004</v>
+        <v>0.76</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -22665,15 +25519,25 @@
       <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="D6" s="13">
+        <v>46265</v>
+      </c>
+      <c r="E6" s="13">
+        <v>46265</v>
+      </c>
+      <c r="F6" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -22699,11 +25563,11 @@
       <c r="J7" s="15"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -22817,7 +25681,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -23681,7 +26545,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.55000000000000004</v>
+        <v>0.76</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -23716,1323 +26580,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50F530F-70D3-4179-810B-A748738D37FC}">
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="15" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="15" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="37"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z2" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="13">
-        <v>46142</v>
-      </c>
-      <c r="E3" s="13">
-        <v>46142</v>
-      </c>
-      <c r="F3" s="20">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0.76</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="14"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46128</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-21.84</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="13">
-        <v>46171</v>
-      </c>
-      <c r="E4" s="13">
-        <v>46171</v>
-      </c>
-      <c r="F4" s="20">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46142</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="13">
-        <v>46203</v>
-      </c>
-      <c r="E5" s="13">
-        <v>46203</v>
-      </c>
-      <c r="F5" s="20">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46171</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="13">
-        <v>46234</v>
-      </c>
-      <c r="E6" s="13">
-        <v>46234</v>
-      </c>
-      <c r="F6" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.22</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46203</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="15"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46234</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>1 m. 0 mėn. 12 d.</v>
-      </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46128</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="15"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46125</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="15"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46505</v>
-      </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="15"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="20">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>268</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="15"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="15"/>
-      <c r="N13" s="14"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="25"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="15"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.12</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="3">
-        <v>21.84</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="13"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="15"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="13"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="15"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="13"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="15"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="13"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="15"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="13"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="15"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="13"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="15"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="13"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="15"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="13"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="15"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="13"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="15"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="13"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="15"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="13"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="15"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="13"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="15"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="13"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="15"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="13"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="15"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="13"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="15"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="13"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="15"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="13"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="15"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="13"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="15"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="13"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="15"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="13"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="15"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="13"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="15"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="13"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="15"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="13"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="15"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="13"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="15"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="13"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="15"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="13"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="15"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="13"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="15"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="13"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="15"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="13"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="15"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="13"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="15"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="13"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="15"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="13"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="15"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="13"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="15"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="13"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="15"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="13"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="15"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="13"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.76</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="39" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="37" priority="9">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="36" priority="10">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>